--- a/data/trans_camb/P1427-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/P1427-Habitat-trans_camb.xlsx
@@ -598,7 +598,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>2,39</t>
+          <t>2,04</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -608,7 +608,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>3,6</t>
+          <t>3,28</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -618,7 +618,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,03</t>
+          <t>2,69</t>
         </is>
       </c>
     </row>
@@ -631,32 +631,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-2,36; 0,55</t>
+          <t>-2,2; 0,48</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,64; 4,03</t>
+          <t>0,29; 3,42</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-2,46; 1,15</t>
+          <t>-2,23; 1,26</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1,78; 5,31</t>
+          <t>1,17; 4,91</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-1,89; 0,42</t>
+          <t>-1,89; 0,43</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,72; 4,16</t>
+          <t>1,33; 3,83</t>
         </is>
       </c>
     </row>
@@ -674,7 +674,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>109,17%</t>
+          <t>93,46%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>119,67%</t>
+          <t>108,99%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -694,7 +694,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>116,58%</t>
+          <t>103,75%</t>
         </is>
       </c>
     </row>
@@ -707,32 +707,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-77,0; 54,3</t>
+          <t>-73,87; 56,88</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>13,22; 275,94</t>
+          <t>6,73; 234,74</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-63,23; 57,63</t>
+          <t>-57,65; 67,43</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>37,8; 277,26</t>
+          <t>25,52; 254,78</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-57,22; 20,52</t>
+          <t>-57,9; 21,11</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>50,0; 205,53</t>
+          <t>38,58; 207,87</t>
         </is>
       </c>
     </row>
@@ -754,7 +754,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>0,48</t>
+          <t>1,0</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -764,7 +764,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>0,52</t>
+          <t>0,44</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -774,7 +774,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>0,46</t>
+          <t>0,72</t>
         </is>
       </c>
     </row>
@@ -787,32 +787,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-2,55; -0,37</t>
+          <t>-2,6; -0,18</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-1,46; 1,82</t>
+          <t>-0,48; 2,44</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-2,26; 0,34</t>
+          <t>-2,42; 0,26</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-0,83; 1,87</t>
+          <t>-0,96; 1,6</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-2,13; -0,28</t>
+          <t>-2,06; -0,3</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-0,84; 1,4</t>
+          <t>-0,27; 1,58</t>
         </is>
       </c>
     </row>
@@ -830,7 +830,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>23,33%</t>
+          <t>48,61%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -840,7 +840,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>19,27%</t>
+          <t>16,37%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -850,7 +850,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>19,39%</t>
+          <t>30,26%</t>
         </is>
       </c>
     </row>
@@ -863,32 +863,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-86,42; -17,9</t>
+          <t>-85,33; -2,53</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-47,92; 126,15</t>
+          <t>-18,01; 203,48</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-67,22; 23,41</t>
+          <t>-67,33; 21,51</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-22,94; 99,68</t>
+          <t>-26,94; 83,15</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-71,6; -13,72</t>
+          <t>-69,38; -12,31</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-27,02; 74,68</t>
+          <t>-9,62; 84,38</t>
         </is>
       </c>
     </row>
@@ -910,7 +910,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0,97</t>
+          <t>0,89</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -920,7 +920,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1,33</t>
+          <t>2,53</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -930,7 +930,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1,23</t>
+          <t>1,71</t>
         </is>
       </c>
     </row>
@@ -943,32 +943,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1,52; 0,75</t>
+          <t>-1,52; 0,8</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-0,31; 2,31</t>
+          <t>-0,4; 2,15</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-1,67; 1,46</t>
+          <t>-1,74; 1,58</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-1,14; 3,01</t>
+          <t>0,78; 4,12</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-1,22; 0,64</t>
+          <t>-1,22; 0,72</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-0,13; 2,36</t>
+          <t>0,68; 2,86</t>
         </is>
       </c>
     </row>
@@ -986,7 +986,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>71,5%</t>
+          <t>65,48%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -996,7 +996,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>61,01%</t>
+          <t>116,0%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1006,7 +1006,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>69,35%</t>
+          <t>96,69%</t>
         </is>
       </c>
     </row>
@@ -1019,32 +1019,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-75,43; 146,34</t>
+          <t>-77,02; 127,11</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-23,43; 273,37</t>
+          <t>-21,66; 283,92</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-55,08; 107,69</t>
+          <t>-59,09; 121,71</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-28,72; 192,5</t>
+          <t>21,47; 295,45</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-55,48; 48,89</t>
+          <t>-53,41; 61,18</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-3,26; 177,17</t>
+          <t>25,59; 233,8</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>0,96</t>
+          <t>0,82</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -1076,7 +1076,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>1,76</t>
+          <t>1,56</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1086,7 +1086,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,4</t>
+          <t>1,21</t>
         </is>
       </c>
     </row>
@@ -1099,32 +1099,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-2,33; 0,12</t>
+          <t>-2,48; 0,05</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-0,5; 2,46</t>
+          <t>-0,6; 2,2</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-1,25; 1,97</t>
+          <t>-1,26; 1,84</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,29; 3,76</t>
+          <t>0,13; 2,98</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-1,35; 0,61</t>
+          <t>-1,44; 0,59</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,26; 2,6</t>
+          <t>0,2; 2,15</t>
         </is>
       </c>
     </row>
@@ -1142,7 +1142,7 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>42,67%</t>
+          <t>36,21%</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -1152,7 +1152,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>65,08%</t>
+          <t>57,73%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>56,19%</t>
+          <t>48,68%</t>
         </is>
       </c>
     </row>
@@ -1175,32 +1175,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-79,01; 9,54</t>
+          <t>-76,97; 8,77</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-17,79; 175,94</t>
+          <t>-21,49; 139,73</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-36,46; 97,07</t>
+          <t>-36,01; 91,04</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>5,69; 178,75</t>
+          <t>2,75; 151,47</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-46,04; 31,43</t>
+          <t>-45,49; 30,0</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>7,32; 133,5</t>
+          <t>5,49; 109,45</t>
         </is>
       </c>
     </row>
@@ -1222,7 +1222,7 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>1,07</t>
+          <t>1,12</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -1232,7 +1232,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>1,64</t>
+          <t>1,79</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1242,7 +1242,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>1,37</t>
+          <t>1,47</t>
         </is>
       </c>
     </row>
@@ -1255,32 +1255,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-1,59; -0,35</t>
+          <t>-1,58; -0,33</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0,11; 1,83</t>
+          <t>0,35; 1,85</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-1,15; 0,37</t>
+          <t>-1,09; 0,38</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0,48; 2,45</t>
+          <t>1,06; 2,5</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-1,17; -0,14</t>
+          <t>-1,09; -0,14</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0,67; 1,92</t>
+          <t>0,9; 1,96</t>
         </is>
       </c>
     </row>
@@ -1298,7 +1298,7 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>53,83%</t>
+          <t>56,63%</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>62,09%</t>
+          <t>67,6%</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -1318,7 +1318,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>58,89%</t>
+          <t>63,27%</t>
         </is>
       </c>
     </row>
@@ -1331,32 +1331,32 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-65,59; -20,24</t>
+          <t>-65,58; -19,53</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>5,28; 111,94</t>
+          <t>14,11; 116,96</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-37,84; 15,16</t>
+          <t>-36,48; 18,73</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>16,11; 109,35</t>
+          <t>33,82; 114,84</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-45,07; -6,62</t>
+          <t>-42,86; -6,16</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>25,34; 93,02</t>
+          <t>35,26; 96,14</t>
         </is>
       </c>
     </row>
